--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.21%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.7%5500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.7%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5500</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.72%1180</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1180</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.86%3340</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.86%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3340</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.03%3865</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.03%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3865</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.44%6815</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6815</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.35%555</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.35%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>555</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.7%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.7%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.4%5645</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5645</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.14%1770</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.14%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1770</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5090</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.75%1295</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.75%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1295</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.2%605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.05%118.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.05%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>118.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:51</t>
+          <t>2026-08-28 06:32:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.49%2055</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.49%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2055</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:57</t>
+          <t>2026-08-28 06:32:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:58</t>
+          <t>2026-08-28 06:32:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:13:59</t>
+          <t>2026-08-28 06:32:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:24</t>
+          <t>2026-08-28 06:58:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:26</t>
+          <t>2026-08-28 06:58:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:27</t>
+          <t>2026-08-28 06:58:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:28</t>
+          <t>2026-08-28 06:58:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2410</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5500</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1180</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.86%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.03%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3865</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.44%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6815</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.35%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>555</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.7%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2090</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.4%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5645</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.14%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1770</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.99%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5090</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+9.75%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1295</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.2%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>605</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.05%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>118.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:00</t>
+          <t>2026-08-28 15:42:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.49%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2055</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1452,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1515,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,17 +1580,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.88%2225</t>
+          <t>+5.39%2345</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1578,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1643,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.43%247.5</t>
+          <t>+9.09%270</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>247.5</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,17 +1706,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.44%960</t>
+          <t>+3.13%990</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1704,7 +1734,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1769,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.96%1030</t>
+          <t>+9.71%1130</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+9.71%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1797,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1832,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.18%617</t>
+          <t>-1.13%610</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.18%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1860,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,17 +1895,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1893,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1958,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1956,7 +1986,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +2021,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>+7.06%235</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>235</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,7 +2049,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,17 +2084,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+4.58%2740</t>
+          <t>-2.19%2680</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2082,7 +2112,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2147,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+0.73%480.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>480.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2210,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.26%206</t>
+          <t>-2.18%201.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2208,7 +2238,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:01</t>
+          <t>2026-08-28 15:42:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2273,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.96%210</t>
+          <t>+2.38%215</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+2.38%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>215</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2336,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1430</v>
+        <v>1365</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2332,7 +2362,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2397,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+8.25%210</t>
+          <t>+3.33%217</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+8.25%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2393,7 +2423,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2458,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.22%83.1</t>
+          <t>+1.93%84.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>83.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2519,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.43%590</t>
+          <t>-1.02%584</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2515,7 +2545,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2580,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.03%19.15</t>
+          <t>-0.52%19.05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2641,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2702,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.27%3870</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3870</v>
+        <v>4065</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2763,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%78.3</t>
+          <t>+0.26%78.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2824,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.68%1480</t>
+          <t>-4.39%1415</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1480</v>
+        <v>1415</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2885,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2946,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.3%333.5</t>
+          <t>-0.3%332.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>333.5</v>
+        <v>332.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +3007,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+4.64%541</t>
+          <t>-0.18%540</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3068,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.73%94.6</t>
+          <t>-2.64%92.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3129,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.33%6105</t>
+          <t>+2.38%6250</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+2.38%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6105</v>
+        <v>6250</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:03</t>
+          <t>2026-08-28 15:43:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3190,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3251,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.95%958</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3312,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+9.91%244</t>
+          <t>-1.23%241</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3373,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.88%90.3</t>
+          <t>+0.22%90.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3434,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+2.23%252</t>
+          <t>+0.4%253</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3495,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.66%151</t>
+          <t>+1.32%153</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:04</t>
+          <t>2026-08-28 15:43:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3556,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.66%146.5</t>
+          <t>+5.12%154</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>+5.12%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>146.5</v>
+        <v>154</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,35 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.87%11,884,000</t>
+          <t>9.29%11,264,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>9.29%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11884000</v>
+        <v>11264000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.11%4,807,000</t>
+          <t>8.99%4,807,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.11%</t>
+          <t>8.99%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.93%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1110</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.25%20,300,000</t>
+          <t>7.68%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.25%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3985</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.88%5,979,000</t>
+          <t>6.99%5,148,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5979000</v>
+        <v>5148000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,27 +748,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.85%5,148,000</t>
+          <t>6.85%5,979,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -785,11 +775,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5148000</v>
+        <v>5979000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,27 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.65%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7200</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.23%2,226,000</t>
+          <t>5.46%2,226,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,27 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.57%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>597</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.85%25,387,000</t>
+          <t>5.17%25,387,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5785</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.73%6,564,000</t>
+          <t>4.75%2,407,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6564000</v>
+        <v>2407000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,40 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.67%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2125</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.68%2,407,000</t>
+          <t>4.75%6,564,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2407000</v>
+        <v>6564000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,27 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.39%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1830</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.42%7,250,000</t>
+          <t>4.52%7,250,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.52%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,27 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5030</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.36%2,486,000</t>
+          <t>4.26%2,486,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1197,40 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.64%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>621</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.29%9,624,000</t>
+          <t>4.12%19,479,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9624000</v>
+        <v>19479000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1260,40 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.25%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1240</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.06%19,479,000</t>
+          <t>4.07%9,624,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>19479000</v>
+        <v>9624000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,27 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>130</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.65%89,518,000</t>
+          <t>3.97%89,518,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:47</t>
+          <t>2026-08-28 17:23:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,27 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.31%4,671,848</t>
+          <t>3.60%4,671,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,12 +1439,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.74%5,498,000</t>
+          <t>2.79%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1512,40 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+5.39%2345</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.80%341,900</t>
+          <t>1.81%2,264,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>341900</v>
+        <v>2264000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1575,40 +1545,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.74%2,264,000</t>
+          <t>1.67%313,900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2264000</v>
+        <v>313900</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,20 +1628,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.00%11,775,450</t>
+          <t>1.17%12,668,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>11775450</v>
+        <v>12668450</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,12 +1691,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.82%2,477,000</t>
+          <t>0.84%2,477,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,12 +1754,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.69%1,957,000</t>
+          <t>0.75%1,957,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1797,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1827,27 +1797,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.13%610</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.67%3,173,000</t>
+          <t>0.67%325,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1856,11 +1826,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3173000</v>
+        <v>325000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1890,27 +1860,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>-1.13%610</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.66%325,000</t>
+          <t>0.66%3,173,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1919,11 +1889,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>325000</v>
+        <v>3173000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,12 +1943,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.59%1,301,000</t>
+          <t>0.56%1,301,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,12 +2006,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.45%5,917,000</t>
+          <t>0.47%5,917,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,12 +2069,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.45%477,000</t>
+          <t>0.44%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,12 +2195,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.23%3,249,000</t>
+          <t>0.22%3,249,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2238,7 +2208,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:42:59</t>
+          <t>2026-08-28 17:23:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2331,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.55%1365</t>
+          <t>+3.33%217</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1365</v>
+        <v>217</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.14%283,000</t>
+          <t>0.13%1,741,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>283000</v>
+        <v>1741000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2392,34 +2362,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3376新日興</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.33%217</t>
+          <t>+1.93%84.7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>217</v>
+        <v>84.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.13%1,741,000</t>
+          <t>0.12%3,988,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1741000</v>
+        <v>3988000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2453,38 +2423,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.93%84.7</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>84.7</v>
+        <v>1365</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.11%3,988,000</t>
+          <t>0.04%88,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3988000</v>
+        <v>88000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2514,25 +2484,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.02%584</t>
+          <t>-0.52%19.05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>584</v>
+        <v>19.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03%140,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2541,7 +2511,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>140000</v>
+        <v>5163000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2575,38 +2545,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.52%19.05</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.05</v>
+        <v>543</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,21 +2606,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.92%543</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>543</v>
+        <v>4065</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2697,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.04%4065</t>
+          <t>+0.26%78.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4065</v>
+        <v>78.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2758,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.26%78.5</t>
+          <t>-4.39%1415</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>78.5</v>
+        <v>1415</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2819,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-4.39%1415</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1415</v>
+        <v>7065</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2880,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>-0.3%332.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7065</v>
+        <v>332.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2941,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.3%332.5</t>
+          <t>-0.18%540</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>332.5</v>
+        <v>540</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3002,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.18%540</t>
+          <t>-2.64%92.1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>540</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3063,21 +3033,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.64%92.1</t>
+          <t>+2.38%6250</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+2.38%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>92.09999999999999</v>
+        <v>6250</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3124,21 +3094,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.38%6250</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6250</v>
+        <v>2010</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:10</t>
+          <t>2026-08-28 17:23:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3185,21 +3155,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2010</v>
+        <v>972</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3246,21 +3216,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.46%972</t>
+          <t>-1.02%584</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>972</v>
+        <v>584</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:21</t>
+          <t>2026-08-28 17:23:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:38</t>
+          <t>2026-08-28 19:05:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:41</t>
+          <t>2026-08-28 19:05:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:43</t>
+          <t>2026-08-28 19:05:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:44</t>
+          <t>2026-08-28 19:06:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:30</t>
+          <t>2026-08-28 20:37:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:41</t>
+          <t>2026-08-28 20:37:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 19:05:52</t>
+          <t>2026-08-28 20:37:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:04</t>
+          <t>2026-08-28 20:37:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2420</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5490</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.93%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1110</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.1%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3985</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.6%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3360</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.65%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7200</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+7.57%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>597</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.48%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5785</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.67%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2125</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.39%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1830</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.18%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5030</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.64%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>621</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.25%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1240</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.7%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>130</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:10</t>
+          <t>2026-08-28 21:39:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.98%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2260</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:21</t>
+          <t>2026-08-28 21:39:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:32</t>
+          <t>2026-08-28 21:39:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:44</t>
+          <t>2026-08-28 21:39:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.93%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1110</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3985</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.65%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7200</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.57%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>597</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5785</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.67%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2125</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+3.39%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1830</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5030</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.64%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>621</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.25%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1240</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>130</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:11</t>
+          <t>2026-08-28 21:45:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.98%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:24</t>
+          <t>2026-08-28 21:45:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:35</t>
+          <t>2026-08-28 21:45:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:47</t>
+          <t>2026-08-28 21:45:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
